--- a/annual/Lasso_Time_Dummy_Models_Annual.xlsx
+++ b/annual/Lasso_Time_Dummy_Models_Annual.xlsx
@@ -11,6 +11,7 @@
     <sheet name="Coefficients" sheetId="2" state="visible" r:id="rId2"/>
     <sheet name="Predictions_By_Product" sheetId="3" state="visible" r:id="rId3"/>
     <sheet name="Jevons_Indices" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Model_Period_Matrix" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -38517,4 +38518,2665 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:EW6"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Apple - iPhone XS Max 64GB</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Apple - iPhone XS Max 256GB</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Apple - iPhone XS Max 512GB</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Apple - iPhone XR 64GB</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Apple - iPhone XR 256GB</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Apple - iPhone XR 128GB</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>Apple - iPhone XS 64GB</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>Apple - iPhone XS 256GB</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>Samsung - Galaxy Note 10 256GB</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>Samsung - Galaxy Note 10+ 512GB</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>Apple - iPhone 11 64GB</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>Apple - iPhone 11 128GB</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>Apple - iPhone 11 Pro 64GB</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>Apple - iPhone 11 256GB</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>Apple - iPhone 11 Pro 256GB</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>Apple - iPhone 11 Pro Max 512GB</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>Apple - iPhone 11 Pro Max 64GB</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>Apple - iPhone 11 Pro 512GB</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>Apple - iPhone 11 Pro Max 256GB</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>Oppo - Find N2 Flip 256GB</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>Samsung - Galaxy Note 10+ 256GB</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>Apple - iPhone XS 512GB</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>OnePlus - OnePlus 7 Pro 5G 256GB</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>OnePlus - OnePlus 8 Pro 256GB</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>Samsung - Galaxy Note 20 Ultra 128GB</t>
+        </is>
+      </c>
+      <c r="AA1" s="1" t="inlineStr">
+        <is>
+          <t>Apple - iPhone 12 Pro Max 256GB</t>
+        </is>
+      </c>
+      <c r="AB1" s="1" t="inlineStr">
+        <is>
+          <t>Apple - iPhone 12 Pro Max 128GB</t>
+        </is>
+      </c>
+      <c r="AC1" s="1" t="inlineStr">
+        <is>
+          <t>Apple - iPhone 12 Pro Max 512GB</t>
+        </is>
+      </c>
+      <c r="AD1" s="1" t="inlineStr">
+        <is>
+          <t>Apple - iPhone 12 Pro 128GB</t>
+        </is>
+      </c>
+      <c r="AE1" s="1" t="inlineStr">
+        <is>
+          <t>Apple - iPhone 12 Pro 512GB</t>
+        </is>
+      </c>
+      <c r="AF1" s="1" t="inlineStr">
+        <is>
+          <t>Apple - iPhone 12 Pro 256GB</t>
+        </is>
+      </c>
+      <c r="AG1" s="1" t="inlineStr">
+        <is>
+          <t>Apple - iPhone 12 mini 128GB</t>
+        </is>
+      </c>
+      <c r="AH1" s="1" t="inlineStr">
+        <is>
+          <t>Apple - iPhone 12 64GB</t>
+        </is>
+      </c>
+      <c r="AI1" s="1" t="inlineStr">
+        <is>
+          <t>Apple - iPhone 12 128GB</t>
+        </is>
+      </c>
+      <c r="AJ1" s="1" t="inlineStr">
+        <is>
+          <t>Apple - iPhone 12 256GB</t>
+        </is>
+      </c>
+      <c r="AK1" s="1" t="inlineStr">
+        <is>
+          <t>Apple - iPhone 12 mini 256GB</t>
+        </is>
+      </c>
+      <c r="AL1" s="1" t="inlineStr">
+        <is>
+          <t>Apple - iPhone 12 mini 64GB</t>
+        </is>
+      </c>
+      <c r="AM1" s="1" t="inlineStr">
+        <is>
+          <t>OnePlus - OnePlus 8 128GB</t>
+        </is>
+      </c>
+      <c r="AN1" s="1" t="inlineStr">
+        <is>
+          <t>OnePlus - OnePlus Nord N10 5G 128GB</t>
+        </is>
+      </c>
+      <c r="AO1" s="1" t="inlineStr">
+        <is>
+          <t>OnePlus - OnePlus 9 Pro 256GB</t>
+        </is>
+      </c>
+      <c r="AP1" s="1" t="inlineStr">
+        <is>
+          <t>OnePlus - OnePlus 9 128GB</t>
+        </is>
+      </c>
+      <c r="AQ1" s="1" t="inlineStr">
+        <is>
+          <t>Samsung - Galaxy Note 20 128GB</t>
+        </is>
+      </c>
+      <c r="AR1" s="1" t="inlineStr">
+        <is>
+          <t>OnePlus - OnePlus Nord 2 5G 128GB</t>
+        </is>
+      </c>
+      <c r="AS1" s="1" t="inlineStr">
+        <is>
+          <t>OnePlus - OnePlus Nord N200 64GB</t>
+        </is>
+      </c>
+      <c r="AT1" s="1" t="inlineStr">
+        <is>
+          <t>OnePlus - OnePlus Nord N100 5G 64GB</t>
+        </is>
+      </c>
+      <c r="AU1" s="1" t="inlineStr">
+        <is>
+          <t>Apple - iPhone 13 mini 512GB</t>
+        </is>
+      </c>
+      <c r="AV1" s="1" t="inlineStr">
+        <is>
+          <t>Apple - iPhone 13 mini 256GB</t>
+        </is>
+      </c>
+      <c r="AW1" s="1" t="inlineStr">
+        <is>
+          <t>Apple - iPhone 13 mini 128GB</t>
+        </is>
+      </c>
+      <c r="AX1" s="1" t="inlineStr">
+        <is>
+          <t>Apple - iPhone 13 256GB</t>
+        </is>
+      </c>
+      <c r="AY1" s="1" t="inlineStr">
+        <is>
+          <t>Apple - iPhone 13 128GB</t>
+        </is>
+      </c>
+      <c r="AZ1" s="1" t="inlineStr">
+        <is>
+          <t>Apple - iPhone 13 512GB</t>
+        </is>
+      </c>
+      <c r="BA1" s="1" t="inlineStr">
+        <is>
+          <t>Apple - iPhone 13 Pro 512GB</t>
+        </is>
+      </c>
+      <c r="BB1" s="1" t="inlineStr">
+        <is>
+          <t>Apple - iPhone 13 Pro Max 512GB</t>
+        </is>
+      </c>
+      <c r="BC1" s="1" t="inlineStr">
+        <is>
+          <t>Apple - iPhone 13 Pro 128GB</t>
+        </is>
+      </c>
+      <c r="BD1" s="1" t="inlineStr">
+        <is>
+          <t>Apple - iPhone 13 Pro Max 128GB</t>
+        </is>
+      </c>
+      <c r="BE1" s="1" t="inlineStr">
+        <is>
+          <t>Apple - iPhone 13 Pro 256GB</t>
+        </is>
+      </c>
+      <c r="BF1" s="1" t="inlineStr">
+        <is>
+          <t>Apple - iPhone 13 Pro Max 256GB</t>
+        </is>
+      </c>
+      <c r="BG1" s="1" t="inlineStr">
+        <is>
+          <t>OnePlus - OnePlus 8T 256GB</t>
+        </is>
+      </c>
+      <c r="BH1" s="1" t="inlineStr">
+        <is>
+          <t>Oppo - Reno7 Pro 5G 256GB</t>
+        </is>
+      </c>
+      <c r="BI1" s="1" t="inlineStr">
+        <is>
+          <t>Oppo - Find X5 256GB</t>
+        </is>
+      </c>
+      <c r="BJ1" s="1" t="inlineStr">
+        <is>
+          <t>Oppo - Find X5 Pro 256GB</t>
+        </is>
+      </c>
+      <c r="BK1" s="1" t="inlineStr">
+        <is>
+          <t>Samsung - Galaxy S22 128GB</t>
+        </is>
+      </c>
+      <c r="BL1" s="1" t="inlineStr">
+        <is>
+          <t>Oppo - Reno7 5G 256GB</t>
+        </is>
+      </c>
+      <c r="BM1" s="1" t="inlineStr">
+        <is>
+          <t>Samsung - Galaxy S22 Ultra 128GB</t>
+        </is>
+      </c>
+      <c r="BN1" s="1" t="inlineStr">
+        <is>
+          <t>Samsung - Galaxy S22+ 128GB</t>
+        </is>
+      </c>
+      <c r="BO1" s="1" t="inlineStr">
+        <is>
+          <t>Samsung - Galaxy S22 256GB</t>
+        </is>
+      </c>
+      <c r="BP1" s="1" t="inlineStr">
+        <is>
+          <t>OnePlus - OnePlus Nord 2T 128GB</t>
+        </is>
+      </c>
+      <c r="BQ1" s="1" t="inlineStr">
+        <is>
+          <t>Oppo - Reno8 5G 128GB</t>
+        </is>
+      </c>
+      <c r="BR1" s="1" t="inlineStr">
+        <is>
+          <t>Samsung - Galaxy Xcover 5 64GB</t>
+        </is>
+      </c>
+      <c r="BS1" s="1" t="inlineStr">
+        <is>
+          <t>Samsung - Galaxy S22 Ultra 256GB</t>
+        </is>
+      </c>
+      <c r="BT1" s="1" t="inlineStr">
+        <is>
+          <t>Samsung - Galaxy S22+ 256GB</t>
+        </is>
+      </c>
+      <c r="BU1" s="1" t="inlineStr">
+        <is>
+          <t>Oppo - Reno8 Pro 5G 256GB</t>
+        </is>
+      </c>
+      <c r="BV1" s="1" t="inlineStr">
+        <is>
+          <t>OnePlus - OnePlus 10 Pro 256GB</t>
+        </is>
+      </c>
+      <c r="BW1" s="1" t="inlineStr">
+        <is>
+          <t>Samsung - Galaxy Z Fold 4 256GB</t>
+        </is>
+      </c>
+      <c r="BX1" s="1" t="inlineStr">
+        <is>
+          <t>Oppo - Reno8 5G 256GB</t>
+        </is>
+      </c>
+      <c r="BY1" s="1" t="inlineStr">
+        <is>
+          <t>Oppo - Reno7 5G 128GB</t>
+        </is>
+      </c>
+      <c r="BZ1" s="1" t="inlineStr">
+        <is>
+          <t>Samsung - Galaxy Z Fold 4 512GB</t>
+        </is>
+      </c>
+      <c r="CA1" s="1" t="inlineStr">
+        <is>
+          <t>Samsung - Galaxy Z Flip 4 256GB</t>
+        </is>
+      </c>
+      <c r="CB1" s="1" t="inlineStr">
+        <is>
+          <t>Samsung - Galaxy Z Flip 4 512GB</t>
+        </is>
+      </c>
+      <c r="CC1" s="1" t="inlineStr">
+        <is>
+          <t>Apple - iPhone 14 128GB</t>
+        </is>
+      </c>
+      <c r="CD1" s="1" t="inlineStr">
+        <is>
+          <t>Apple - iPhone 14 256GB</t>
+        </is>
+      </c>
+      <c r="CE1" s="1" t="inlineStr">
+        <is>
+          <t>Apple - iPhone 14 512GB</t>
+        </is>
+      </c>
+      <c r="CF1" s="1" t="inlineStr">
+        <is>
+          <t>Apple - iPhone 14 Pro Max 256GB</t>
+        </is>
+      </c>
+      <c r="CG1" s="1" t="inlineStr">
+        <is>
+          <t>Apple - iPhone 14 Plus 128GB</t>
+        </is>
+      </c>
+      <c r="CH1" s="1" t="inlineStr">
+        <is>
+          <t>Apple - iPhone 14 Pro Max 128GB</t>
+        </is>
+      </c>
+      <c r="CI1" s="1" t="inlineStr">
+        <is>
+          <t>Apple - iPhone 14 Plus 256GB</t>
+        </is>
+      </c>
+      <c r="CJ1" s="1" t="inlineStr">
+        <is>
+          <t>Apple - iPhone 14 Pro Max 512GB</t>
+        </is>
+      </c>
+      <c r="CK1" s="1" t="inlineStr">
+        <is>
+          <t>Apple - iPhone 14 Pro 128GB</t>
+        </is>
+      </c>
+      <c r="CL1" s="1" t="inlineStr">
+        <is>
+          <t>Apple - iPhone 14 Pro 256GB</t>
+        </is>
+      </c>
+      <c r="CM1" s="1" t="inlineStr">
+        <is>
+          <t>Apple - iPhone 14 Pro 512GB</t>
+        </is>
+      </c>
+      <c r="CN1" s="1" t="inlineStr">
+        <is>
+          <t>Apple - iPhone 14 Plus 512GB</t>
+        </is>
+      </c>
+      <c r="CO1" s="1" t="inlineStr">
+        <is>
+          <t>OnePlus - OnePlus 11 256GB</t>
+        </is>
+      </c>
+      <c r="CP1" s="1" t="inlineStr">
+        <is>
+          <t>Samsung - Galaxy Xcover 6 Pro 128GB</t>
+        </is>
+      </c>
+      <c r="CQ1" s="1" t="inlineStr">
+        <is>
+          <t>Samsung - Galaxy A04 64GB</t>
+        </is>
+      </c>
+      <c r="CR1" s="1" t="inlineStr">
+        <is>
+          <t>Samsung - Galaxy A34 256GB</t>
+        </is>
+      </c>
+      <c r="CS1" s="1" t="inlineStr">
+        <is>
+          <t>OnePlus - OnePlus Nord CE 3 Lite 256GB</t>
+        </is>
+      </c>
+      <c r="CT1" s="1" t="inlineStr">
+        <is>
+          <t>Samsung - Galaxy A24 128GB</t>
+        </is>
+      </c>
+      <c r="CU1" s="1" t="inlineStr">
+        <is>
+          <t>Samsung - Galaxy A54 128GB</t>
+        </is>
+      </c>
+      <c r="CV1" s="1" t="inlineStr">
+        <is>
+          <t>Samsung - Galaxy S23+ 256GB</t>
+        </is>
+      </c>
+      <c r="CW1" s="1" t="inlineStr">
+        <is>
+          <t>Samsung - Galaxy S23 Ultra 256GB</t>
+        </is>
+      </c>
+      <c r="CX1" s="1" t="inlineStr">
+        <is>
+          <t>Samsung - Galaxy S23 128GB</t>
+        </is>
+      </c>
+      <c r="CY1" s="1" t="inlineStr">
+        <is>
+          <t>Samsung - Galaxy A54 256GB</t>
+        </is>
+      </c>
+      <c r="CZ1" s="1" t="inlineStr">
+        <is>
+          <t>Samsung - Galaxy S23 256GB</t>
+        </is>
+      </c>
+      <c r="DA1" s="1" t="inlineStr">
+        <is>
+          <t>OnePlus - OnePlus 10T 5G 256GB</t>
+        </is>
+      </c>
+      <c r="DB1" s="1" t="inlineStr">
+        <is>
+          <t>Oppo - Reno10 5G 256GB</t>
+        </is>
+      </c>
+      <c r="DC1" s="1" t="inlineStr">
+        <is>
+          <t>Oppo - Reno10 Pro 5G 256GB</t>
+        </is>
+      </c>
+      <c r="DD1" s="1" t="inlineStr">
+        <is>
+          <t>Samsung - Galaxy Z Flip 5 512GB</t>
+        </is>
+      </c>
+      <c r="DE1" s="1" t="inlineStr">
+        <is>
+          <t>Samsung - Galaxy Z Fold 5 512GB</t>
+        </is>
+      </c>
+      <c r="DF1" s="1" t="inlineStr">
+        <is>
+          <t>OnePlus - OnePlus Nord N30 5G 128GB</t>
+        </is>
+      </c>
+      <c r="DG1" s="1" t="inlineStr">
+        <is>
+          <t>Samsung - Galaxy S24 128GB</t>
+        </is>
+      </c>
+      <c r="DH1" s="1" t="inlineStr">
+        <is>
+          <t>Samsung - Galaxy S24 256GB</t>
+        </is>
+      </c>
+      <c r="DI1" s="1" t="inlineStr">
+        <is>
+          <t>Apple - iPhone 15 256GB</t>
+        </is>
+      </c>
+      <c r="DJ1" s="1" t="inlineStr">
+        <is>
+          <t>Apple - iPhone 15 512GB</t>
+        </is>
+      </c>
+      <c r="DK1" s="1" t="inlineStr">
+        <is>
+          <t>Apple - iPhone 15 128GB</t>
+        </is>
+      </c>
+      <c r="DL1" s="1" t="inlineStr">
+        <is>
+          <t>Apple - iPhone 15 Plus 512GB</t>
+        </is>
+      </c>
+      <c r="DM1" s="1" t="inlineStr">
+        <is>
+          <t>Apple - iPhone 15 Plus 256GB</t>
+        </is>
+      </c>
+      <c r="DN1" s="1" t="inlineStr">
+        <is>
+          <t>Apple - iPhone 15 Plus 128GB</t>
+        </is>
+      </c>
+      <c r="DO1" s="1" t="inlineStr">
+        <is>
+          <t>Apple - iPhone 15 Pro 512GB</t>
+        </is>
+      </c>
+      <c r="DP1" s="1" t="inlineStr">
+        <is>
+          <t>Apple - iPhone 15 Pro Max 512GB</t>
+        </is>
+      </c>
+      <c r="DQ1" s="1" t="inlineStr">
+        <is>
+          <t>Apple - iPhone 15 Pro Max 256GB</t>
+        </is>
+      </c>
+      <c r="DR1" s="1" t="inlineStr">
+        <is>
+          <t>Apple - iPhone 15 Pro 128GB</t>
+        </is>
+      </c>
+      <c r="DS1" s="1" t="inlineStr">
+        <is>
+          <t>Apple - iPhone 15 Pro 256GB</t>
+        </is>
+      </c>
+      <c r="DT1" s="1" t="inlineStr">
+        <is>
+          <t>Samsung - Galaxy Z Flip 5 256GB</t>
+        </is>
+      </c>
+      <c r="DU1" s="1" t="inlineStr">
+        <is>
+          <t>OnePlus - OnePlus 12R 256GB</t>
+        </is>
+      </c>
+      <c r="DV1" s="1" t="inlineStr">
+        <is>
+          <t>Oppo - Reno11 Pro 512GB</t>
+        </is>
+      </c>
+      <c r="DW1" s="1" t="inlineStr">
+        <is>
+          <t>Oppo - Reno11 F 256GB</t>
+        </is>
+      </c>
+      <c r="DX1" s="1" t="inlineStr">
+        <is>
+          <t>Oppo - A60 256GB</t>
+        </is>
+      </c>
+      <c r="DY1" s="1" t="inlineStr">
+        <is>
+          <t>OnePlus - OnePlus 12 256GB</t>
+        </is>
+      </c>
+      <c r="DZ1" s="1" t="inlineStr">
+        <is>
+          <t>Samsung - Galaxy S24 Ultra 256GB</t>
+        </is>
+      </c>
+      <c r="EA1" s="1" t="inlineStr">
+        <is>
+          <t>Apple - iPhone X 64GB</t>
+        </is>
+      </c>
+      <c r="EB1" s="1" t="inlineStr">
+        <is>
+          <t>Samsung - Galaxy S24+ 256GB</t>
+        </is>
+      </c>
+      <c r="EC1" s="1" t="inlineStr">
+        <is>
+          <t>Oppo - Reno12 256GB</t>
+        </is>
+      </c>
+      <c r="ED1" s="1" t="inlineStr">
+        <is>
+          <t>Oppo - Reno12 Pro 512GB</t>
+        </is>
+      </c>
+      <c r="EE1" s="1" t="inlineStr">
+        <is>
+          <t>Oppo - Reno12 F 4G 256GB</t>
+        </is>
+      </c>
+      <c r="EF1" s="1" t="inlineStr">
+        <is>
+          <t>Oppo - A80 256GB</t>
+        </is>
+      </c>
+      <c r="EG1" s="1" t="inlineStr">
+        <is>
+          <t>Samsung - Galaxy Z Fold 5 256GB</t>
+        </is>
+      </c>
+      <c r="EH1" s="1" t="inlineStr">
+        <is>
+          <t>Apple - iPhone 16 256GB</t>
+        </is>
+      </c>
+      <c r="EI1" s="1" t="inlineStr">
+        <is>
+          <t>Apple - iPhone 16 Pro 512GB</t>
+        </is>
+      </c>
+      <c r="EJ1" s="1" t="inlineStr">
+        <is>
+          <t>Apple - iPhone 16 Plus 512GB</t>
+        </is>
+      </c>
+      <c r="EK1" s="1" t="inlineStr">
+        <is>
+          <t>Apple - iPhone 16 Plus 256GB</t>
+        </is>
+      </c>
+      <c r="EL1" s="1" t="inlineStr">
+        <is>
+          <t>Apple - iPhone 16 Pro Max 256GB</t>
+        </is>
+      </c>
+      <c r="EM1" s="1" t="inlineStr">
+        <is>
+          <t>Apple - iPhone 16 Plus 128GB</t>
+        </is>
+      </c>
+      <c r="EN1" s="1" t="inlineStr">
+        <is>
+          <t>Apple - iPhone 16 Pro 256GB</t>
+        </is>
+      </c>
+      <c r="EO1" s="1" t="inlineStr">
+        <is>
+          <t>Apple - iPhone 16 Pro 128GB</t>
+        </is>
+      </c>
+      <c r="EP1" s="1" t="inlineStr">
+        <is>
+          <t>Apple - iPhone 16 128GB</t>
+        </is>
+      </c>
+      <c r="EQ1" s="1" t="inlineStr">
+        <is>
+          <t>Apple - iPhone 16 512GB</t>
+        </is>
+      </c>
+      <c r="ER1" s="1" t="inlineStr">
+        <is>
+          <t>Oppo - Find X8 Pro 512GB</t>
+        </is>
+      </c>
+      <c r="ES1" s="1" t="inlineStr">
+        <is>
+          <t>Apple - iPhone 16 Pro Max 512GB</t>
+        </is>
+      </c>
+      <c r="ET1" s="1" t="inlineStr">
+        <is>
+          <t>Oppo - Reno13 F 4G 256GB</t>
+        </is>
+      </c>
+      <c r="EU1" s="1" t="inlineStr">
+        <is>
+          <t>Oppo - Reno13 256GB</t>
+        </is>
+      </c>
+      <c r="EV1" s="1" t="inlineStr">
+        <is>
+          <t>Oppo - Reno13 Pro 512GB</t>
+        </is>
+      </c>
+      <c r="EW1" s="1" t="inlineStr">
+        <is>
+          <t>Oppo - A60 128GB</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="1" t="inlineStr">
+        <is>
+          <t>2020→2021</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>-0.2273794562155356</v>
+      </c>
+      <c r="C2" t="n">
+        <v>-0.2273794562155356</v>
+      </c>
+      <c r="D2" t="n">
+        <v>-0.2273794562155356</v>
+      </c>
+      <c r="E2" t="n">
+        <v>-0.2273794562155356</v>
+      </c>
+      <c r="F2" t="n">
+        <v>-0.2273794562155356</v>
+      </c>
+      <c r="G2" t="n">
+        <v>-0.2273794562155356</v>
+      </c>
+      <c r="H2" t="n">
+        <v>-0.2273794562155365</v>
+      </c>
+      <c r="I2" t="n">
+        <v>-0.2273794562155365</v>
+      </c>
+      <c r="J2" t="n">
+        <v>-0.2273794562155356</v>
+      </c>
+      <c r="K2" t="n">
+        <v>-0.2273794562155365</v>
+      </c>
+      <c r="L2" t="n">
+        <v>-0.2273794562155365</v>
+      </c>
+      <c r="M2" t="n">
+        <v>-0.2273794562155365</v>
+      </c>
+      <c r="N2" t="n">
+        <v>-0.2273794562155356</v>
+      </c>
+      <c r="O2" t="n">
+        <v>-0.2273794562155365</v>
+      </c>
+      <c r="P2" t="n">
+        <v>-0.2273794562155356</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>-0.2273794562155365</v>
+      </c>
+      <c r="R2" t="n">
+        <v>-0.2273794562155365</v>
+      </c>
+      <c r="S2" t="n">
+        <v>-0.2273794562155356</v>
+      </c>
+      <c r="T2" t="n">
+        <v>-0.2273794562155365</v>
+      </c>
+      <c r="U2" t="inlineStr"/>
+      <c r="V2" t="n">
+        <v>-0.2273794562155365</v>
+      </c>
+      <c r="W2" t="n">
+        <v>-0.2273794562155365</v>
+      </c>
+      <c r="X2" t="n">
+        <v>-0.2273794562155356</v>
+      </c>
+      <c r="Y2" t="n">
+        <v>-0.2273794562155365</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>-0.2273794562155356</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>-0.2273794562155356</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>-0.2273794562155356</v>
+      </c>
+      <c r="AC2" t="n">
+        <v>-0.2273794562155356</v>
+      </c>
+      <c r="AD2" t="n">
+        <v>-0.2273794562155365</v>
+      </c>
+      <c r="AE2" t="n">
+        <v>-0.2273794562155365</v>
+      </c>
+      <c r="AF2" t="n">
+        <v>-0.2273794562155365</v>
+      </c>
+      <c r="AG2" t="n">
+        <v>-0.2273794562155365</v>
+      </c>
+      <c r="AH2" t="n">
+        <v>-0.2273794562155356</v>
+      </c>
+      <c r="AI2" t="n">
+        <v>-0.2273794562155356</v>
+      </c>
+      <c r="AJ2" t="n">
+        <v>-0.2273794562155356</v>
+      </c>
+      <c r="AK2" t="n">
+        <v>-0.2273794562155365</v>
+      </c>
+      <c r="AL2" t="n">
+        <v>-0.2273794562155365</v>
+      </c>
+      <c r="AM2" t="n">
+        <v>-0.2273794562155356</v>
+      </c>
+      <c r="AN2" t="n">
+        <v>-0.2273794562155356</v>
+      </c>
+      <c r="AO2" t="n">
+        <v>-0.2273794562155365</v>
+      </c>
+      <c r="AP2" t="n">
+        <v>-0.2273794562155356</v>
+      </c>
+      <c r="AQ2" t="n">
+        <v>-0.2273794562155356</v>
+      </c>
+      <c r="AR2" t="inlineStr"/>
+      <c r="AS2" t="n">
+        <v>-0.2273794562155365</v>
+      </c>
+      <c r="AT2" t="n">
+        <v>-0.2273794562155365</v>
+      </c>
+      <c r="AU2" t="inlineStr"/>
+      <c r="AV2" t="inlineStr"/>
+      <c r="AW2" t="n">
+        <v>-0.2273794562155365</v>
+      </c>
+      <c r="AX2" t="inlineStr"/>
+      <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr"/>
+      <c r="BA2" t="inlineStr"/>
+      <c r="BB2" t="n">
+        <v>-0.2273794562155356</v>
+      </c>
+      <c r="BC2" t="inlineStr"/>
+      <c r="BD2" t="inlineStr"/>
+      <c r="BE2" t="n">
+        <v>-0.2273794562155365</v>
+      </c>
+      <c r="BF2" t="n">
+        <v>-0.2273794562155356</v>
+      </c>
+      <c r="BG2" t="inlineStr"/>
+      <c r="BH2" t="inlineStr"/>
+      <c r="BI2" t="inlineStr"/>
+      <c r="BJ2" t="inlineStr"/>
+      <c r="BK2" t="inlineStr"/>
+      <c r="BL2" t="inlineStr"/>
+      <c r="BM2" t="inlineStr"/>
+      <c r="BN2" t="inlineStr"/>
+      <c r="BO2" t="inlineStr"/>
+      <c r="BP2" t="inlineStr"/>
+      <c r="BQ2" t="inlineStr"/>
+      <c r="BR2" t="inlineStr"/>
+      <c r="BS2" t="inlineStr"/>
+      <c r="BT2" t="inlineStr"/>
+      <c r="BU2" t="inlineStr"/>
+      <c r="BV2" t="inlineStr"/>
+      <c r="BW2" t="inlineStr"/>
+      <c r="BX2" t="inlineStr"/>
+      <c r="BY2" t="inlineStr"/>
+      <c r="BZ2" t="inlineStr"/>
+      <c r="CA2" t="inlineStr"/>
+      <c r="CB2" t="inlineStr"/>
+      <c r="CC2" t="inlineStr"/>
+      <c r="CD2" t="inlineStr"/>
+      <c r="CE2" t="inlineStr"/>
+      <c r="CF2" t="inlineStr"/>
+      <c r="CG2" t="inlineStr"/>
+      <c r="CH2" t="inlineStr"/>
+      <c r="CI2" t="inlineStr"/>
+      <c r="CJ2" t="inlineStr"/>
+      <c r="CK2" t="inlineStr"/>
+      <c r="CL2" t="inlineStr"/>
+      <c r="CM2" t="inlineStr"/>
+      <c r="CN2" t="inlineStr"/>
+      <c r="CO2" t="inlineStr"/>
+      <c r="CP2" t="inlineStr"/>
+      <c r="CQ2" t="inlineStr"/>
+      <c r="CR2" t="inlineStr"/>
+      <c r="CS2" t="inlineStr"/>
+      <c r="CT2" t="inlineStr"/>
+      <c r="CU2" t="inlineStr"/>
+      <c r="CV2" t="inlineStr"/>
+      <c r="CW2" t="inlineStr"/>
+      <c r="CX2" t="inlineStr"/>
+      <c r="CY2" t="inlineStr"/>
+      <c r="CZ2" t="inlineStr"/>
+      <c r="DA2" t="inlineStr"/>
+      <c r="DB2" t="inlineStr"/>
+      <c r="DC2" t="inlineStr"/>
+      <c r="DD2" t="inlineStr"/>
+      <c r="DE2" t="inlineStr"/>
+      <c r="DF2" t="inlineStr"/>
+      <c r="DG2" t="inlineStr"/>
+      <c r="DH2" t="inlineStr"/>
+      <c r="DI2" t="inlineStr"/>
+      <c r="DJ2" t="inlineStr"/>
+      <c r="DK2" t="inlineStr"/>
+      <c r="DL2" t="inlineStr"/>
+      <c r="DM2" t="inlineStr"/>
+      <c r="DN2" t="inlineStr"/>
+      <c r="DO2" t="inlineStr"/>
+      <c r="DP2" t="inlineStr"/>
+      <c r="DQ2" t="inlineStr"/>
+      <c r="DR2" t="inlineStr"/>
+      <c r="DS2" t="inlineStr"/>
+      <c r="DT2" t="inlineStr"/>
+      <c r="DU2" t="inlineStr"/>
+      <c r="DV2" t="inlineStr"/>
+      <c r="DW2" t="inlineStr"/>
+      <c r="DX2" t="inlineStr"/>
+      <c r="DY2" t="inlineStr"/>
+      <c r="DZ2" t="inlineStr"/>
+      <c r="EA2" t="inlineStr"/>
+      <c r="EB2" t="inlineStr"/>
+      <c r="EC2" t="inlineStr"/>
+      <c r="ED2" t="inlineStr"/>
+      <c r="EE2" t="inlineStr"/>
+      <c r="EF2" t="inlineStr"/>
+      <c r="EG2" t="inlineStr"/>
+      <c r="EH2" t="inlineStr"/>
+      <c r="EI2" t="inlineStr"/>
+      <c r="EJ2" t="inlineStr"/>
+      <c r="EK2" t="inlineStr"/>
+      <c r="EL2" t="inlineStr"/>
+      <c r="EM2" t="inlineStr"/>
+      <c r="EN2" t="inlineStr"/>
+      <c r="EO2" t="inlineStr"/>
+      <c r="EP2" t="inlineStr"/>
+      <c r="EQ2" t="inlineStr"/>
+      <c r="ER2" t="inlineStr"/>
+      <c r="ES2" t="inlineStr"/>
+      <c r="ET2" t="inlineStr"/>
+      <c r="EU2" t="inlineStr"/>
+      <c r="EV2" t="inlineStr"/>
+      <c r="EW2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" s="1" t="inlineStr">
+        <is>
+          <t>2021→2022</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>-0.1418017032069443</v>
+      </c>
+      <c r="C3" t="n">
+        <v>-0.1418017032069443</v>
+      </c>
+      <c r="D3" t="n">
+        <v>-0.1418017032069443</v>
+      </c>
+      <c r="E3" t="n">
+        <v>-0.1418017032069443</v>
+      </c>
+      <c r="F3" t="n">
+        <v>-0.1418017032069443</v>
+      </c>
+      <c r="G3" t="n">
+        <v>-0.1418017032069443</v>
+      </c>
+      <c r="H3" t="n">
+        <v>-0.1418017032069443</v>
+      </c>
+      <c r="I3" t="n">
+        <v>-0.1418017032069443</v>
+      </c>
+      <c r="J3" t="n">
+        <v>-0.1418017032069443</v>
+      </c>
+      <c r="K3" t="n">
+        <v>-0.1418017032069443</v>
+      </c>
+      <c r="L3" t="n">
+        <v>-0.1418017032069443</v>
+      </c>
+      <c r="M3" t="n">
+        <v>-0.1418017032069443</v>
+      </c>
+      <c r="N3" t="n">
+        <v>-0.1418017032069443</v>
+      </c>
+      <c r="O3" t="n">
+        <v>-0.1418017032069443</v>
+      </c>
+      <c r="P3" t="n">
+        <v>-0.1418017032069443</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>-0.1418017032069443</v>
+      </c>
+      <c r="R3" t="n">
+        <v>-0.1418017032069443</v>
+      </c>
+      <c r="S3" t="n">
+        <v>-0.1418017032069443</v>
+      </c>
+      <c r="T3" t="n">
+        <v>-0.1418017032069443</v>
+      </c>
+      <c r="U3" t="inlineStr"/>
+      <c r="V3" t="n">
+        <v>-0.1418017032069443</v>
+      </c>
+      <c r="W3" t="n">
+        <v>-0.1418017032069443</v>
+      </c>
+      <c r="X3" t="n">
+        <v>-0.1418017032069443</v>
+      </c>
+      <c r="Y3" t="n">
+        <v>-0.1418017032069443</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>-0.1418017032069443</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>-0.1418017032069443</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>-0.1418017032069443</v>
+      </c>
+      <c r="AC3" t="n">
+        <v>-0.1418017032069443</v>
+      </c>
+      <c r="AD3" t="n">
+        <v>-0.1418017032069443</v>
+      </c>
+      <c r="AE3" t="n">
+        <v>-0.1418017032069443</v>
+      </c>
+      <c r="AF3" t="n">
+        <v>-0.1418017032069443</v>
+      </c>
+      <c r="AG3" t="n">
+        <v>-0.1418017032069443</v>
+      </c>
+      <c r="AH3" t="n">
+        <v>-0.1418017032069443</v>
+      </c>
+      <c r="AI3" t="n">
+        <v>-0.1418017032069443</v>
+      </c>
+      <c r="AJ3" t="n">
+        <v>-0.1418017032069443</v>
+      </c>
+      <c r="AK3" t="n">
+        <v>-0.1418017032069443</v>
+      </c>
+      <c r="AL3" t="n">
+        <v>-0.1418017032069443</v>
+      </c>
+      <c r="AM3" t="n">
+        <v>-0.1418017032069443</v>
+      </c>
+      <c r="AN3" t="n">
+        <v>-0.1418017032069443</v>
+      </c>
+      <c r="AO3" t="n">
+        <v>-0.1418017032069443</v>
+      </c>
+      <c r="AP3" t="n">
+        <v>-0.1418017032069443</v>
+      </c>
+      <c r="AQ3" t="n">
+        <v>-0.1418017032069443</v>
+      </c>
+      <c r="AR3" t="n">
+        <v>-0.1418017032069443</v>
+      </c>
+      <c r="AS3" t="n">
+        <v>-0.1418017032069443</v>
+      </c>
+      <c r="AT3" t="n">
+        <v>-0.1418017032069443</v>
+      </c>
+      <c r="AU3" t="n">
+        <v>-0.1418017032069443</v>
+      </c>
+      <c r="AV3" t="n">
+        <v>-0.1418017032069443</v>
+      </c>
+      <c r="AW3" t="n">
+        <v>-0.1418017032069443</v>
+      </c>
+      <c r="AX3" t="n">
+        <v>-0.1418017032069443</v>
+      </c>
+      <c r="AY3" t="n">
+        <v>-0.1418017032069443</v>
+      </c>
+      <c r="AZ3" t="n">
+        <v>-0.1418017032069443</v>
+      </c>
+      <c r="BA3" t="n">
+        <v>-0.1418017032069443</v>
+      </c>
+      <c r="BB3" t="n">
+        <v>-0.1418017032069443</v>
+      </c>
+      <c r="BC3" t="n">
+        <v>-0.1418017032069443</v>
+      </c>
+      <c r="BD3" t="n">
+        <v>-0.1418017032069443</v>
+      </c>
+      <c r="BE3" t="n">
+        <v>-0.1418017032069443</v>
+      </c>
+      <c r="BF3" t="n">
+        <v>-0.1418017032069443</v>
+      </c>
+      <c r="BG3" t="n">
+        <v>-0.1418017032069443</v>
+      </c>
+      <c r="BH3" t="n">
+        <v>-0.1418017032069443</v>
+      </c>
+      <c r="BI3" t="n">
+        <v>-0.1418017032069443</v>
+      </c>
+      <c r="BJ3" t="n">
+        <v>-0.1418017032069443</v>
+      </c>
+      <c r="BK3" t="n">
+        <v>-0.1418017032069443</v>
+      </c>
+      <c r="BL3" t="n">
+        <v>-0.1418017032069443</v>
+      </c>
+      <c r="BM3" t="n">
+        <v>-0.1418017032069443</v>
+      </c>
+      <c r="BN3" t="n">
+        <v>-0.1418017032069443</v>
+      </c>
+      <c r="BO3" t="n">
+        <v>-0.1418017032069443</v>
+      </c>
+      <c r="BP3" t="n">
+        <v>-0.1418017032069443</v>
+      </c>
+      <c r="BQ3" t="n">
+        <v>-0.1418017032069443</v>
+      </c>
+      <c r="BR3" t="n">
+        <v>-0.1418017032069443</v>
+      </c>
+      <c r="BS3" t="n">
+        <v>-0.1418017032069443</v>
+      </c>
+      <c r="BT3" t="n">
+        <v>-0.1418017032069443</v>
+      </c>
+      <c r="BU3" t="n">
+        <v>-0.1418017032069443</v>
+      </c>
+      <c r="BV3" t="inlineStr"/>
+      <c r="BW3" t="n">
+        <v>-0.1418017032069443</v>
+      </c>
+      <c r="BX3" t="n">
+        <v>-0.1418017032069443</v>
+      </c>
+      <c r="BY3" t="inlineStr"/>
+      <c r="BZ3" t="n">
+        <v>-0.1418017032069443</v>
+      </c>
+      <c r="CA3" t="n">
+        <v>-0.1418017032069443</v>
+      </c>
+      <c r="CB3" t="n">
+        <v>-0.1418017032069443</v>
+      </c>
+      <c r="CC3" t="n">
+        <v>-0.1418017032069443</v>
+      </c>
+      <c r="CD3" t="n">
+        <v>-0.1418017032069443</v>
+      </c>
+      <c r="CE3" t="n">
+        <v>-0.1418017032069443</v>
+      </c>
+      <c r="CF3" t="n">
+        <v>-0.1418017032069443</v>
+      </c>
+      <c r="CG3" t="n">
+        <v>-0.1418017032069443</v>
+      </c>
+      <c r="CH3" t="n">
+        <v>-0.1418017032069443</v>
+      </c>
+      <c r="CI3" t="inlineStr"/>
+      <c r="CJ3" t="n">
+        <v>-0.1418017032069443</v>
+      </c>
+      <c r="CK3" t="n">
+        <v>-0.1418017032069443</v>
+      </c>
+      <c r="CL3" t="n">
+        <v>-0.1418017032069443</v>
+      </c>
+      <c r="CM3" t="n">
+        <v>-0.1418017032069443</v>
+      </c>
+      <c r="CN3" t="inlineStr"/>
+      <c r="CO3" t="inlineStr"/>
+      <c r="CP3" t="inlineStr"/>
+      <c r="CQ3" t="inlineStr"/>
+      <c r="CR3" t="inlineStr"/>
+      <c r="CS3" t="inlineStr"/>
+      <c r="CT3" t="inlineStr"/>
+      <c r="CU3" t="inlineStr"/>
+      <c r="CV3" t="inlineStr"/>
+      <c r="CW3" t="inlineStr"/>
+      <c r="CX3" t="inlineStr"/>
+      <c r="CY3" t="inlineStr"/>
+      <c r="CZ3" t="inlineStr"/>
+      <c r="DA3" t="inlineStr"/>
+      <c r="DB3" t="inlineStr"/>
+      <c r="DC3" t="inlineStr"/>
+      <c r="DD3" t="inlineStr"/>
+      <c r="DE3" t="inlineStr"/>
+      <c r="DF3" t="inlineStr"/>
+      <c r="DG3" t="inlineStr"/>
+      <c r="DH3" t="inlineStr"/>
+      <c r="DI3" t="inlineStr"/>
+      <c r="DJ3" t="inlineStr"/>
+      <c r="DK3" t="inlineStr"/>
+      <c r="DL3" t="inlineStr"/>
+      <c r="DM3" t="inlineStr"/>
+      <c r="DN3" t="inlineStr"/>
+      <c r="DO3" t="inlineStr"/>
+      <c r="DP3" t="inlineStr"/>
+      <c r="DQ3" t="inlineStr"/>
+      <c r="DR3" t="inlineStr"/>
+      <c r="DS3" t="inlineStr"/>
+      <c r="DT3" t="inlineStr"/>
+      <c r="DU3" t="inlineStr"/>
+      <c r="DV3" t="inlineStr"/>
+      <c r="DW3" t="inlineStr"/>
+      <c r="DX3" t="inlineStr"/>
+      <c r="DY3" t="inlineStr"/>
+      <c r="DZ3" t="inlineStr"/>
+      <c r="EA3" t="inlineStr"/>
+      <c r="EB3" t="inlineStr"/>
+      <c r="EC3" t="inlineStr"/>
+      <c r="ED3" t="inlineStr"/>
+      <c r="EE3" t="inlineStr"/>
+      <c r="EF3" t="inlineStr"/>
+      <c r="EG3" t="inlineStr"/>
+      <c r="EH3" t="inlineStr"/>
+      <c r="EI3" t="inlineStr"/>
+      <c r="EJ3" t="inlineStr"/>
+      <c r="EK3" t="inlineStr"/>
+      <c r="EL3" t="inlineStr"/>
+      <c r="EM3" t="inlineStr"/>
+      <c r="EN3" t="inlineStr"/>
+      <c r="EO3" t="inlineStr"/>
+      <c r="EP3" t="inlineStr"/>
+      <c r="EQ3" t="inlineStr"/>
+      <c r="ER3" t="inlineStr"/>
+      <c r="ES3" t="inlineStr"/>
+      <c r="ET3" t="inlineStr"/>
+      <c r="EU3" t="inlineStr"/>
+      <c r="EV3" t="inlineStr"/>
+      <c r="EW3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>2022→2023</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>-0.1717656642648215</v>
+      </c>
+      <c r="C4" t="n">
+        <v>-0.1717656642648215</v>
+      </c>
+      <c r="D4" t="n">
+        <v>-0.1717656642648215</v>
+      </c>
+      <c r="E4" t="n">
+        <v>-0.1717656642648224</v>
+      </c>
+      <c r="F4" t="n">
+        <v>-0.1717656642648224</v>
+      </c>
+      <c r="G4" t="n">
+        <v>-0.1717656642648224</v>
+      </c>
+      <c r="H4" t="n">
+        <v>-0.1717656642648215</v>
+      </c>
+      <c r="I4" t="n">
+        <v>-0.1717656642648215</v>
+      </c>
+      <c r="J4" t="n">
+        <v>-0.1717656642648224</v>
+      </c>
+      <c r="K4" t="n">
+        <v>-0.1717656642648224</v>
+      </c>
+      <c r="L4" t="n">
+        <v>-0.1717656642648215</v>
+      </c>
+      <c r="M4" t="n">
+        <v>-0.1717656642648215</v>
+      </c>
+      <c r="N4" t="n">
+        <v>-0.1717656642648224</v>
+      </c>
+      <c r="O4" t="n">
+        <v>-0.1717656642648215</v>
+      </c>
+      <c r="P4" t="n">
+        <v>-0.1717656642648224</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>-0.1717656642648215</v>
+      </c>
+      <c r="R4" t="n">
+        <v>-0.1717656642648215</v>
+      </c>
+      <c r="S4" t="n">
+        <v>-0.1717656642648224</v>
+      </c>
+      <c r="T4" t="n">
+        <v>-0.1717656642648215</v>
+      </c>
+      <c r="U4" t="n">
+        <v>-0.1717656642648215</v>
+      </c>
+      <c r="V4" t="n">
+        <v>-0.1717656642648224</v>
+      </c>
+      <c r="W4" t="n">
+        <v>-0.1717656642648215</v>
+      </c>
+      <c r="X4" t="n">
+        <v>-0.1717656642648215</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>-0.1717656642648215</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>-0.1717656642648224</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>-0.1717656642648215</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>-0.1717656642648215</v>
+      </c>
+      <c r="AC4" t="n">
+        <v>-0.1717656642648215</v>
+      </c>
+      <c r="AD4" t="n">
+        <v>-0.1717656642648215</v>
+      </c>
+      <c r="AE4" t="n">
+        <v>-0.1717656642648215</v>
+      </c>
+      <c r="AF4" t="n">
+        <v>-0.1717656642648215</v>
+      </c>
+      <c r="AG4" t="n">
+        <v>-0.1717656642648224</v>
+      </c>
+      <c r="AH4" t="n">
+        <v>-0.1717656642648224</v>
+      </c>
+      <c r="AI4" t="n">
+        <v>-0.1717656642648224</v>
+      </c>
+      <c r="AJ4" t="n">
+        <v>-0.1717656642648224</v>
+      </c>
+      <c r="AK4" t="n">
+        <v>-0.1717656642648224</v>
+      </c>
+      <c r="AL4" t="n">
+        <v>-0.1717656642648224</v>
+      </c>
+      <c r="AM4" t="n">
+        <v>-0.1717656642648215</v>
+      </c>
+      <c r="AN4" t="n">
+        <v>-0.1717656642648215</v>
+      </c>
+      <c r="AO4" t="n">
+        <v>-0.1717656642648215</v>
+      </c>
+      <c r="AP4" t="n">
+        <v>-0.1717656642648215</v>
+      </c>
+      <c r="AQ4" t="n">
+        <v>-0.1717656642648224</v>
+      </c>
+      <c r="AR4" t="n">
+        <v>-0.1717656642648215</v>
+      </c>
+      <c r="AS4" t="n">
+        <v>-0.1717656642648224</v>
+      </c>
+      <c r="AT4" t="n">
+        <v>-0.1717656642648215</v>
+      </c>
+      <c r="AU4" t="n">
+        <v>-0.1717656642648224</v>
+      </c>
+      <c r="AV4" t="n">
+        <v>-0.1717656642648224</v>
+      </c>
+      <c r="AW4" t="n">
+        <v>-0.1717656642648224</v>
+      </c>
+      <c r="AX4" t="n">
+        <v>-0.1717656642648215</v>
+      </c>
+      <c r="AY4" t="n">
+        <v>-0.1717656642648215</v>
+      </c>
+      <c r="AZ4" t="n">
+        <v>-0.1717656642648215</v>
+      </c>
+      <c r="BA4" t="n">
+        <v>-0.1717656642648224</v>
+      </c>
+      <c r="BB4" t="n">
+        <v>-0.1717656642648215</v>
+      </c>
+      <c r="BC4" t="n">
+        <v>-0.1717656642648224</v>
+      </c>
+      <c r="BD4" t="n">
+        <v>-0.1717656642648215</v>
+      </c>
+      <c r="BE4" t="n">
+        <v>-0.1717656642648224</v>
+      </c>
+      <c r="BF4" t="n">
+        <v>-0.1717656642648215</v>
+      </c>
+      <c r="BG4" t="n">
+        <v>-0.1717656642648215</v>
+      </c>
+      <c r="BH4" t="n">
+        <v>-0.1717656642648224</v>
+      </c>
+      <c r="BI4" t="n">
+        <v>-0.1717656642648215</v>
+      </c>
+      <c r="BJ4" t="n">
+        <v>-0.1717656642648224</v>
+      </c>
+      <c r="BK4" t="n">
+        <v>-0.1717656642648215</v>
+      </c>
+      <c r="BL4" t="n">
+        <v>-0.1717656642648224</v>
+      </c>
+      <c r="BM4" t="n">
+        <v>-0.1717656642648215</v>
+      </c>
+      <c r="BN4" t="n">
+        <v>-0.1717656642648215</v>
+      </c>
+      <c r="BO4" t="n">
+        <v>-0.1717656642648215</v>
+      </c>
+      <c r="BP4" t="n">
+        <v>-0.1717656642648215</v>
+      </c>
+      <c r="BQ4" t="n">
+        <v>-0.1717656642648224</v>
+      </c>
+      <c r="BR4" t="n">
+        <v>-0.1717656642648224</v>
+      </c>
+      <c r="BS4" t="n">
+        <v>-0.1717656642648215</v>
+      </c>
+      <c r="BT4" t="n">
+        <v>-0.1717656642648224</v>
+      </c>
+      <c r="BU4" t="n">
+        <v>-0.1717656642648224</v>
+      </c>
+      <c r="BV4" t="n">
+        <v>-0.1717656642648215</v>
+      </c>
+      <c r="BW4" t="n">
+        <v>-0.1717656642648215</v>
+      </c>
+      <c r="BX4" t="n">
+        <v>-0.1717656642648215</v>
+      </c>
+      <c r="BY4" t="n">
+        <v>-0.1717656642648215</v>
+      </c>
+      <c r="BZ4" t="n">
+        <v>-0.1717656642648224</v>
+      </c>
+      <c r="CA4" t="n">
+        <v>-0.1717656642648215</v>
+      </c>
+      <c r="CB4" t="n">
+        <v>-0.1717656642648215</v>
+      </c>
+      <c r="CC4" t="n">
+        <v>-0.1717656642648215</v>
+      </c>
+      <c r="CD4" t="n">
+        <v>-0.1717656642648215</v>
+      </c>
+      <c r="CE4" t="n">
+        <v>-0.1717656642648215</v>
+      </c>
+      <c r="CF4" t="n">
+        <v>-0.1717656642648215</v>
+      </c>
+      <c r="CG4" t="n">
+        <v>-0.1717656642648215</v>
+      </c>
+      <c r="CH4" t="n">
+        <v>-0.1717656642648215</v>
+      </c>
+      <c r="CI4" t="n">
+        <v>-0.1717656642648215</v>
+      </c>
+      <c r="CJ4" t="n">
+        <v>-0.1717656642648215</v>
+      </c>
+      <c r="CK4" t="n">
+        <v>-0.1717656642648215</v>
+      </c>
+      <c r="CL4" t="n">
+        <v>-0.1717656642648215</v>
+      </c>
+      <c r="CM4" t="n">
+        <v>-0.1717656642648215</v>
+      </c>
+      <c r="CN4" t="n">
+        <v>-0.1717656642648215</v>
+      </c>
+      <c r="CO4" t="n">
+        <v>-0.1717656642648215</v>
+      </c>
+      <c r="CP4" t="n">
+        <v>-0.1717656642648215</v>
+      </c>
+      <c r="CQ4" t="n">
+        <v>-0.1717656642648215</v>
+      </c>
+      <c r="CR4" t="n">
+        <v>-0.1717656642648215</v>
+      </c>
+      <c r="CS4" t="n">
+        <v>-0.1717656642648215</v>
+      </c>
+      <c r="CT4" t="n">
+        <v>-0.1717656642648215</v>
+      </c>
+      <c r="CU4" t="n">
+        <v>-0.1717656642648215</v>
+      </c>
+      <c r="CV4" t="n">
+        <v>-0.1717656642648215</v>
+      </c>
+      <c r="CW4" t="n">
+        <v>-0.1717656642648215</v>
+      </c>
+      <c r="CX4" t="n">
+        <v>-0.1717656642648215</v>
+      </c>
+      <c r="CY4" t="n">
+        <v>-0.1717656642648215</v>
+      </c>
+      <c r="CZ4" t="n">
+        <v>-0.1717656642648215</v>
+      </c>
+      <c r="DA4" t="inlineStr"/>
+      <c r="DB4" t="n">
+        <v>-0.1717656642648215</v>
+      </c>
+      <c r="DC4" t="inlineStr"/>
+      <c r="DD4" t="n">
+        <v>-0.1717656642648215</v>
+      </c>
+      <c r="DE4" t="n">
+        <v>-0.1717656642648215</v>
+      </c>
+      <c r="DF4" t="n">
+        <v>-0.1717656642648215</v>
+      </c>
+      <c r="DG4" t="inlineStr"/>
+      <c r="DH4" t="inlineStr"/>
+      <c r="DI4" t="n">
+        <v>-0.1717656642648215</v>
+      </c>
+      <c r="DJ4" t="n">
+        <v>-0.1717656642648215</v>
+      </c>
+      <c r="DK4" t="n">
+        <v>-0.1717656642648215</v>
+      </c>
+      <c r="DL4" t="inlineStr"/>
+      <c r="DM4" t="n">
+        <v>-0.1717656642648224</v>
+      </c>
+      <c r="DN4" t="n">
+        <v>-0.1717656642648224</v>
+      </c>
+      <c r="DO4" t="n">
+        <v>-0.1717656642648215</v>
+      </c>
+      <c r="DP4" t="n">
+        <v>-0.1717656642648215</v>
+      </c>
+      <c r="DQ4" t="n">
+        <v>-0.1717656642648215</v>
+      </c>
+      <c r="DR4" t="n">
+        <v>-0.1717656642648215</v>
+      </c>
+      <c r="DS4" t="n">
+        <v>-0.1717656642648215</v>
+      </c>
+      <c r="DT4" t="n">
+        <v>-0.1717656642648215</v>
+      </c>
+      <c r="DU4" t="inlineStr"/>
+      <c r="DV4" t="inlineStr"/>
+      <c r="DW4" t="inlineStr"/>
+      <c r="DX4" t="inlineStr"/>
+      <c r="DY4" t="inlineStr"/>
+      <c r="DZ4" t="inlineStr"/>
+      <c r="EA4" t="inlineStr"/>
+      <c r="EB4" t="inlineStr"/>
+      <c r="EC4" t="inlineStr"/>
+      <c r="ED4" t="inlineStr"/>
+      <c r="EE4" t="inlineStr"/>
+      <c r="EF4" t="inlineStr"/>
+      <c r="EG4" t="inlineStr"/>
+      <c r="EH4" t="inlineStr"/>
+      <c r="EI4" t="inlineStr"/>
+      <c r="EJ4" t="inlineStr"/>
+      <c r="EK4" t="inlineStr"/>
+      <c r="EL4" t="inlineStr"/>
+      <c r="EM4" t="inlineStr"/>
+      <c r="EN4" t="inlineStr"/>
+      <c r="EO4" t="inlineStr"/>
+      <c r="EP4" t="inlineStr"/>
+      <c r="EQ4" t="inlineStr"/>
+      <c r="ER4" t="inlineStr"/>
+      <c r="ES4" t="inlineStr"/>
+      <c r="ET4" t="inlineStr"/>
+      <c r="EU4" t="inlineStr"/>
+      <c r="EV4" t="inlineStr"/>
+      <c r="EW4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="inlineStr">
+        <is>
+          <t>2023→2024</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>-0.1717257086693698</v>
+      </c>
+      <c r="C5" t="n">
+        <v>-0.1717257086693698</v>
+      </c>
+      <c r="D5" t="n">
+        <v>-0.1717257086693698</v>
+      </c>
+      <c r="E5" t="n">
+        <v>-0.1717257086693706</v>
+      </c>
+      <c r="F5" t="n">
+        <v>-0.1717257086693706</v>
+      </c>
+      <c r="G5" t="n">
+        <v>-0.1717257086693706</v>
+      </c>
+      <c r="H5" t="n">
+        <v>-0.1717257086693706</v>
+      </c>
+      <c r="I5" t="n">
+        <v>-0.1717257086693706</v>
+      </c>
+      <c r="J5" t="n">
+        <v>-0.1717257086693698</v>
+      </c>
+      <c r="K5" t="n">
+        <v>-0.1717257086693706</v>
+      </c>
+      <c r="L5" t="n">
+        <v>-0.1717257086693706</v>
+      </c>
+      <c r="M5" t="n">
+        <v>-0.1717257086693706</v>
+      </c>
+      <c r="N5" t="n">
+        <v>-0.1717257086693706</v>
+      </c>
+      <c r="O5" t="n">
+        <v>-0.1717257086693706</v>
+      </c>
+      <c r="P5" t="n">
+        <v>-0.1717257086693706</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>-0.1717257086693698</v>
+      </c>
+      <c r="R5" t="n">
+        <v>-0.1717257086693698</v>
+      </c>
+      <c r="S5" t="n">
+        <v>-0.1717257086693706</v>
+      </c>
+      <c r="T5" t="n">
+        <v>-0.1717257086693698</v>
+      </c>
+      <c r="U5" t="n">
+        <v>-0.1717257086693698</v>
+      </c>
+      <c r="V5" t="n">
+        <v>-0.1717257086693706</v>
+      </c>
+      <c r="W5" t="n">
+        <v>-0.1717257086693706</v>
+      </c>
+      <c r="X5" t="n">
+        <v>-0.1717257086693706</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>-0.1717257086693706</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>-0.1717257086693706</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>-0.1717257086693706</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>-0.1717257086693706</v>
+      </c>
+      <c r="AC5" t="n">
+        <v>-0.1717257086693706</v>
+      </c>
+      <c r="AD5" t="n">
+        <v>-0.1717257086693698</v>
+      </c>
+      <c r="AE5" t="n">
+        <v>-0.1717257086693698</v>
+      </c>
+      <c r="AF5" t="n">
+        <v>-0.1717257086693698</v>
+      </c>
+      <c r="AG5" t="n">
+        <v>-0.1717257086693706</v>
+      </c>
+      <c r="AH5" t="n">
+        <v>-0.1717257086693698</v>
+      </c>
+      <c r="AI5" t="n">
+        <v>-0.1717257086693698</v>
+      </c>
+      <c r="AJ5" t="n">
+        <v>-0.1717257086693698</v>
+      </c>
+      <c r="AK5" t="n">
+        <v>-0.1717257086693706</v>
+      </c>
+      <c r="AL5" t="n">
+        <v>-0.1717257086693706</v>
+      </c>
+      <c r="AM5" t="n">
+        <v>-0.1717257086693698</v>
+      </c>
+      <c r="AN5" t="n">
+        <v>-0.1717257086693706</v>
+      </c>
+      <c r="AO5" t="n">
+        <v>-0.1717257086693706</v>
+      </c>
+      <c r="AP5" t="n">
+        <v>-0.1717257086693706</v>
+      </c>
+      <c r="AQ5" t="n">
+        <v>-0.1717257086693706</v>
+      </c>
+      <c r="AR5" t="n">
+        <v>-0.1717257086693698</v>
+      </c>
+      <c r="AS5" t="n">
+        <v>-0.1717257086693706</v>
+      </c>
+      <c r="AT5" t="n">
+        <v>-0.1717257086693706</v>
+      </c>
+      <c r="AU5" t="n">
+        <v>-0.1717257086693698</v>
+      </c>
+      <c r="AV5" t="n">
+        <v>-0.1717257086693698</v>
+      </c>
+      <c r="AW5" t="n">
+        <v>-0.1717257086693698</v>
+      </c>
+      <c r="AX5" t="n">
+        <v>-0.1717257086693698</v>
+      </c>
+      <c r="AY5" t="n">
+        <v>-0.1717257086693698</v>
+      </c>
+      <c r="AZ5" t="n">
+        <v>-0.1717257086693698</v>
+      </c>
+      <c r="BA5" t="n">
+        <v>-0.1717257086693706</v>
+      </c>
+      <c r="BB5" t="n">
+        <v>-0.1717257086693706</v>
+      </c>
+      <c r="BC5" t="n">
+        <v>-0.1717257086693706</v>
+      </c>
+      <c r="BD5" t="n">
+        <v>-0.1717257086693706</v>
+      </c>
+      <c r="BE5" t="n">
+        <v>-0.1717257086693706</v>
+      </c>
+      <c r="BF5" t="n">
+        <v>-0.1717257086693706</v>
+      </c>
+      <c r="BG5" t="n">
+        <v>-0.1717257086693706</v>
+      </c>
+      <c r="BH5" t="n">
+        <v>-0.1717257086693706</v>
+      </c>
+      <c r="BI5" t="n">
+        <v>-0.1717257086693706</v>
+      </c>
+      <c r="BJ5" t="n">
+        <v>-0.1717257086693698</v>
+      </c>
+      <c r="BK5" t="n">
+        <v>-0.1717257086693706</v>
+      </c>
+      <c r="BL5" t="n">
+        <v>-0.1717257086693706</v>
+      </c>
+      <c r="BM5" t="n">
+        <v>-0.1717257086693706</v>
+      </c>
+      <c r="BN5" t="n">
+        <v>-0.1717257086693706</v>
+      </c>
+      <c r="BO5" t="n">
+        <v>-0.1717257086693706</v>
+      </c>
+      <c r="BP5" t="n">
+        <v>-0.1717257086693706</v>
+      </c>
+      <c r="BQ5" t="n">
+        <v>-0.1717257086693698</v>
+      </c>
+      <c r="BR5" t="n">
+        <v>-0.1717257086693698</v>
+      </c>
+      <c r="BS5" t="n">
+        <v>-0.1717257086693706</v>
+      </c>
+      <c r="BT5" t="n">
+        <v>-0.1717257086693698</v>
+      </c>
+      <c r="BU5" t="n">
+        <v>-0.1717257086693698</v>
+      </c>
+      <c r="BV5" t="n">
+        <v>-0.1717257086693698</v>
+      </c>
+      <c r="BW5" t="n">
+        <v>-0.1717257086693706</v>
+      </c>
+      <c r="BX5" t="n">
+        <v>-0.1717257086693698</v>
+      </c>
+      <c r="BY5" t="n">
+        <v>-0.1717257086693706</v>
+      </c>
+      <c r="BZ5" t="n">
+        <v>-0.1717257086693706</v>
+      </c>
+      <c r="CA5" t="n">
+        <v>-0.1717257086693706</v>
+      </c>
+      <c r="CB5" t="n">
+        <v>-0.1717257086693698</v>
+      </c>
+      <c r="CC5" t="n">
+        <v>-0.1717257086693706</v>
+      </c>
+      <c r="CD5" t="n">
+        <v>-0.1717257086693706</v>
+      </c>
+      <c r="CE5" t="n">
+        <v>-0.1717257086693706</v>
+      </c>
+      <c r="CF5" t="n">
+        <v>-0.1717257086693698</v>
+      </c>
+      <c r="CG5" t="n">
+        <v>-0.1717257086693706</v>
+      </c>
+      <c r="CH5" t="n">
+        <v>-0.1717257086693698</v>
+      </c>
+      <c r="CI5" t="n">
+        <v>-0.1717257086693706</v>
+      </c>
+      <c r="CJ5" t="n">
+        <v>-0.1717257086693698</v>
+      </c>
+      <c r="CK5" t="n">
+        <v>-0.1717257086693698</v>
+      </c>
+      <c r="CL5" t="n">
+        <v>-0.1717257086693706</v>
+      </c>
+      <c r="CM5" t="n">
+        <v>-0.1717257086693706</v>
+      </c>
+      <c r="CN5" t="n">
+        <v>-0.1717257086693706</v>
+      </c>
+      <c r="CO5" t="n">
+        <v>-0.1717257086693706</v>
+      </c>
+      <c r="CP5" t="n">
+        <v>-0.1717257086693706</v>
+      </c>
+      <c r="CQ5" t="n">
+        <v>-0.1717257086693698</v>
+      </c>
+      <c r="CR5" t="n">
+        <v>-0.1717257086693698</v>
+      </c>
+      <c r="CS5" t="n">
+        <v>-0.1717257086693706</v>
+      </c>
+      <c r="CT5" t="n">
+        <v>-0.1717257086693706</v>
+      </c>
+      <c r="CU5" t="n">
+        <v>-0.1717257086693706</v>
+      </c>
+      <c r="CV5" t="n">
+        <v>-0.1717257086693698</v>
+      </c>
+      <c r="CW5" t="n">
+        <v>-0.1717257086693706</v>
+      </c>
+      <c r="CX5" t="n">
+        <v>-0.1717257086693706</v>
+      </c>
+      <c r="CY5" t="n">
+        <v>-0.1717257086693706</v>
+      </c>
+      <c r="CZ5" t="n">
+        <v>-0.1717257086693706</v>
+      </c>
+      <c r="DA5" t="n">
+        <v>-0.1717257086693706</v>
+      </c>
+      <c r="DB5" t="n">
+        <v>-0.1717257086693706</v>
+      </c>
+      <c r="DC5" t="n">
+        <v>-0.1717257086693706</v>
+      </c>
+      <c r="DD5" t="n">
+        <v>-0.1717257086693706</v>
+      </c>
+      <c r="DE5" t="n">
+        <v>-0.1717257086693698</v>
+      </c>
+      <c r="DF5" t="n">
+        <v>-0.1717257086693706</v>
+      </c>
+      <c r="DG5" t="n">
+        <v>-0.1717257086693706</v>
+      </c>
+      <c r="DH5" t="n">
+        <v>-0.1717257086693706</v>
+      </c>
+      <c r="DI5" t="n">
+        <v>-0.1717257086693706</v>
+      </c>
+      <c r="DJ5" t="n">
+        <v>-0.1717257086693706</v>
+      </c>
+      <c r="DK5" t="n">
+        <v>-0.1717257086693706</v>
+      </c>
+      <c r="DL5" t="n">
+        <v>-0.1717257086693698</v>
+      </c>
+      <c r="DM5" t="n">
+        <v>-0.1717257086693698</v>
+      </c>
+      <c r="DN5" t="n">
+        <v>-0.1717257086693698</v>
+      </c>
+      <c r="DO5" t="n">
+        <v>-0.1717257086693698</v>
+      </c>
+      <c r="DP5" t="n">
+        <v>-0.1717257086693698</v>
+      </c>
+      <c r="DQ5" t="n">
+        <v>-0.1717257086693698</v>
+      </c>
+      <c r="DR5" t="n">
+        <v>-0.1717257086693698</v>
+      </c>
+      <c r="DS5" t="n">
+        <v>-0.1717257086693698</v>
+      </c>
+      <c r="DT5" t="n">
+        <v>-0.1717257086693706</v>
+      </c>
+      <c r="DU5" t="n">
+        <v>-0.1717257086693706</v>
+      </c>
+      <c r="DV5" t="n">
+        <v>-0.1717257086693706</v>
+      </c>
+      <c r="DW5" t="n">
+        <v>-0.1717257086693706</v>
+      </c>
+      <c r="DX5" t="inlineStr"/>
+      <c r="DY5" t="inlineStr"/>
+      <c r="DZ5" t="n">
+        <v>-0.1717257086693706</v>
+      </c>
+      <c r="EA5" t="n">
+        <v>-0.1717257086693706</v>
+      </c>
+      <c r="EB5" t="n">
+        <v>-0.1717257086693706</v>
+      </c>
+      <c r="EC5" t="inlineStr"/>
+      <c r="ED5" t="inlineStr"/>
+      <c r="EE5" t="n">
+        <v>-0.1717257086693698</v>
+      </c>
+      <c r="EF5" t="inlineStr"/>
+      <c r="EG5" t="n">
+        <v>-0.1717257086693706</v>
+      </c>
+      <c r="EH5" t="n">
+        <v>-0.1717257086693706</v>
+      </c>
+      <c r="EI5" t="n">
+        <v>-0.1717257086693698</v>
+      </c>
+      <c r="EJ5" t="n">
+        <v>-0.1717257086693698</v>
+      </c>
+      <c r="EK5" t="n">
+        <v>-0.1717257086693698</v>
+      </c>
+      <c r="EL5" t="n">
+        <v>-0.1717257086693706</v>
+      </c>
+      <c r="EM5" t="n">
+        <v>-0.1717257086693698</v>
+      </c>
+      <c r="EN5" t="n">
+        <v>-0.1717257086693698</v>
+      </c>
+      <c r="EO5" t="n">
+        <v>-0.1717257086693698</v>
+      </c>
+      <c r="EP5" t="n">
+        <v>-0.1717257086693706</v>
+      </c>
+      <c r="EQ5" t="n">
+        <v>-0.1717257086693706</v>
+      </c>
+      <c r="ER5" t="inlineStr"/>
+      <c r="ES5" t="n">
+        <v>-0.1717257086693706</v>
+      </c>
+      <c r="ET5" t="inlineStr"/>
+      <c r="EU5" t="inlineStr"/>
+      <c r="EV5" t="inlineStr"/>
+      <c r="EW5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="inlineStr">
+        <is>
+          <t>2024→2025</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>-0.1285327585743037</v>
+      </c>
+      <c r="C6" t="n">
+        <v>-0.1285327585743037</v>
+      </c>
+      <c r="D6" t="n">
+        <v>-0.1285327585743037</v>
+      </c>
+      <c r="E6" t="n">
+        <v>-0.1285327585743037</v>
+      </c>
+      <c r="F6" t="n">
+        <v>-0.1285327585743037</v>
+      </c>
+      <c r="G6" t="n">
+        <v>-0.1285327585743037</v>
+      </c>
+      <c r="H6" t="n">
+        <v>-0.1285327585743037</v>
+      </c>
+      <c r="I6" t="n">
+        <v>-0.1285327585743037</v>
+      </c>
+      <c r="J6" t="n">
+        <v>-0.1285327585743046</v>
+      </c>
+      <c r="K6" t="n">
+        <v>-0.1285327585743037</v>
+      </c>
+      <c r="L6" t="n">
+        <v>-0.1285327585743037</v>
+      </c>
+      <c r="M6" t="n">
+        <v>-0.1285327585743037</v>
+      </c>
+      <c r="N6" t="n">
+        <v>-0.1285327585743037</v>
+      </c>
+      <c r="O6" t="n">
+        <v>-0.1285327585743037</v>
+      </c>
+      <c r="P6" t="n">
+        <v>-0.1285327585743037</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>-0.1285327585743037</v>
+      </c>
+      <c r="R6" t="n">
+        <v>-0.1285327585743037</v>
+      </c>
+      <c r="S6" t="n">
+        <v>-0.1285327585743037</v>
+      </c>
+      <c r="T6" t="n">
+        <v>-0.1285327585743037</v>
+      </c>
+      <c r="U6" t="n">
+        <v>-0.1285327585743037</v>
+      </c>
+      <c r="V6" t="n">
+        <v>-0.1285327585743037</v>
+      </c>
+      <c r="W6" t="n">
+        <v>-0.1285327585743037</v>
+      </c>
+      <c r="X6" t="n">
+        <v>-0.1285327585743037</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>-0.1285327585743037</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>-0.1285327585743037</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>-0.1285327585743037</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>-0.1285327585743037</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>-0.1285327585743037</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>-0.1285327585743046</v>
+      </c>
+      <c r="AE6" t="n">
+        <v>-0.1285327585743046</v>
+      </c>
+      <c r="AF6" t="n">
+        <v>-0.1285327585743046</v>
+      </c>
+      <c r="AG6" t="n">
+        <v>-0.1285327585743037</v>
+      </c>
+      <c r="AH6" t="n">
+        <v>-0.1285327585743037</v>
+      </c>
+      <c r="AI6" t="n">
+        <v>-0.1285327585743037</v>
+      </c>
+      <c r="AJ6" t="n">
+        <v>-0.1285327585743037</v>
+      </c>
+      <c r="AK6" t="n">
+        <v>-0.1285327585743037</v>
+      </c>
+      <c r="AL6" t="n">
+        <v>-0.1285327585743037</v>
+      </c>
+      <c r="AM6" t="n">
+        <v>-0.1285327585743037</v>
+      </c>
+      <c r="AN6" t="n">
+        <v>-0.1285327585743037</v>
+      </c>
+      <c r="AO6" t="n">
+        <v>-0.1285327585743037</v>
+      </c>
+      <c r="AP6" t="n">
+        <v>-0.1285327585743037</v>
+      </c>
+      <c r="AQ6" t="n">
+        <v>-0.1285327585743037</v>
+      </c>
+      <c r="AR6" t="n">
+        <v>-0.1285327585743037</v>
+      </c>
+      <c r="AS6" t="n">
+        <v>-0.1285327585743037</v>
+      </c>
+      <c r="AT6" t="n">
+        <v>-0.1285327585743046</v>
+      </c>
+      <c r="AU6" t="n">
+        <v>-0.1285327585743037</v>
+      </c>
+      <c r="AV6" t="n">
+        <v>-0.1285327585743037</v>
+      </c>
+      <c r="AW6" t="n">
+        <v>-0.1285327585743037</v>
+      </c>
+      <c r="AX6" t="n">
+        <v>-0.1285327585743046</v>
+      </c>
+      <c r="AY6" t="n">
+        <v>-0.1285327585743046</v>
+      </c>
+      <c r="AZ6" t="n">
+        <v>-0.1285327585743046</v>
+      </c>
+      <c r="BA6" t="n">
+        <v>-0.1285327585743037</v>
+      </c>
+      <c r="BB6" t="n">
+        <v>-0.1285327585743037</v>
+      </c>
+      <c r="BC6" t="n">
+        <v>-0.1285327585743037</v>
+      </c>
+      <c r="BD6" t="n">
+        <v>-0.1285327585743037</v>
+      </c>
+      <c r="BE6" t="n">
+        <v>-0.1285327585743037</v>
+      </c>
+      <c r="BF6" t="n">
+        <v>-0.1285327585743037</v>
+      </c>
+      <c r="BG6" t="n">
+        <v>-0.1285327585743046</v>
+      </c>
+      <c r="BH6" t="n">
+        <v>-0.1285327585743046</v>
+      </c>
+      <c r="BI6" t="n">
+        <v>-0.1285327585743037</v>
+      </c>
+      <c r="BJ6" t="n">
+        <v>-0.1285327585743037</v>
+      </c>
+      <c r="BK6" t="n">
+        <v>-0.1285327585743037</v>
+      </c>
+      <c r="BL6" t="n">
+        <v>-0.1285327585743037</v>
+      </c>
+      <c r="BM6" t="n">
+        <v>-0.1285327585743037</v>
+      </c>
+      <c r="BN6" t="n">
+        <v>-0.1285327585743037</v>
+      </c>
+      <c r="BO6" t="n">
+        <v>-0.1285327585743037</v>
+      </c>
+      <c r="BP6" t="n">
+        <v>-0.1285327585743046</v>
+      </c>
+      <c r="BQ6" t="n">
+        <v>-0.1285327585743037</v>
+      </c>
+      <c r="BR6" t="n">
+        <v>-0.1285327585743037</v>
+      </c>
+      <c r="BS6" t="n">
+        <v>-0.1285327585743037</v>
+      </c>
+      <c r="BT6" t="n">
+        <v>-0.1285327585743037</v>
+      </c>
+      <c r="BU6" t="n">
+        <v>-0.1285327585743037</v>
+      </c>
+      <c r="BV6" t="n">
+        <v>-0.1285327585743037</v>
+      </c>
+      <c r="BW6" t="n">
+        <v>-0.1285327585743037</v>
+      </c>
+      <c r="BX6" t="n">
+        <v>-0.1285327585743037</v>
+      </c>
+      <c r="BY6" t="n">
+        <v>-0.1285327585743037</v>
+      </c>
+      <c r="BZ6" t="n">
+        <v>-0.1285327585743037</v>
+      </c>
+      <c r="CA6" t="n">
+        <v>-0.1285327585743037</v>
+      </c>
+      <c r="CB6" t="n">
+        <v>-0.1285327585743037</v>
+      </c>
+      <c r="CC6" t="n">
+        <v>-0.1285327585743046</v>
+      </c>
+      <c r="CD6" t="n">
+        <v>-0.1285327585743046</v>
+      </c>
+      <c r="CE6" t="n">
+        <v>-0.1285327585743046</v>
+      </c>
+      <c r="CF6" t="n">
+        <v>-0.1285327585743037</v>
+      </c>
+      <c r="CG6" t="n">
+        <v>-0.1285327585743037</v>
+      </c>
+      <c r="CH6" t="n">
+        <v>-0.1285327585743046</v>
+      </c>
+      <c r="CI6" t="n">
+        <v>-0.1285327585743037</v>
+      </c>
+      <c r="CJ6" t="n">
+        <v>-0.1285327585743037</v>
+      </c>
+      <c r="CK6" t="n">
+        <v>-0.1285327585743037</v>
+      </c>
+      <c r="CL6" t="n">
+        <v>-0.1285327585743046</v>
+      </c>
+      <c r="CM6" t="n">
+        <v>-0.1285327585743046</v>
+      </c>
+      <c r="CN6" t="n">
+        <v>-0.1285327585743037</v>
+      </c>
+      <c r="CO6" t="n">
+        <v>-0.1285327585743046</v>
+      </c>
+      <c r="CP6" t="n">
+        <v>-0.1285327585743037</v>
+      </c>
+      <c r="CQ6" t="n">
+        <v>-0.1285327585743037</v>
+      </c>
+      <c r="CR6" t="n">
+        <v>-0.1285327585743037</v>
+      </c>
+      <c r="CS6" t="n">
+        <v>-0.1285327585743046</v>
+      </c>
+      <c r="CT6" t="n">
+        <v>-0.1285327585743037</v>
+      </c>
+      <c r="CU6" t="n">
+        <v>-0.1285327585743037</v>
+      </c>
+      <c r="CV6" t="n">
+        <v>-0.1285327585743037</v>
+      </c>
+      <c r="CW6" t="n">
+        <v>-0.1285327585743037</v>
+      </c>
+      <c r="CX6" t="n">
+        <v>-0.1285327585743037</v>
+      </c>
+      <c r="CY6" t="n">
+        <v>-0.1285327585743037</v>
+      </c>
+      <c r="CZ6" t="n">
+        <v>-0.1285327585743037</v>
+      </c>
+      <c r="DA6" t="n">
+        <v>-0.1285327585743037</v>
+      </c>
+      <c r="DB6" t="n">
+        <v>-0.1285327585743046</v>
+      </c>
+      <c r="DC6" t="n">
+        <v>-0.1285327585743037</v>
+      </c>
+      <c r="DD6" t="n">
+        <v>-0.1285327585743037</v>
+      </c>
+      <c r="DE6" t="n">
+        <v>-0.1285327585743046</v>
+      </c>
+      <c r="DF6" t="n">
+        <v>-0.1285327585743037</v>
+      </c>
+      <c r="DG6" t="n">
+        <v>-0.1285327585743037</v>
+      </c>
+      <c r="DH6" t="n">
+        <v>-0.1285327585743037</v>
+      </c>
+      <c r="DI6" t="n">
+        <v>-0.1285327585743037</v>
+      </c>
+      <c r="DJ6" t="n">
+        <v>-0.1285327585743037</v>
+      </c>
+      <c r="DK6" t="n">
+        <v>-0.1285327585743037</v>
+      </c>
+      <c r="DL6" t="n">
+        <v>-0.1285327585743037</v>
+      </c>
+      <c r="DM6" t="n">
+        <v>-0.1285327585743037</v>
+      </c>
+      <c r="DN6" t="n">
+        <v>-0.1285327585743037</v>
+      </c>
+      <c r="DO6" t="n">
+        <v>-0.1285327585743037</v>
+      </c>
+      <c r="DP6" t="n">
+        <v>-0.1285327585743037</v>
+      </c>
+      <c r="DQ6" t="n">
+        <v>-0.1285327585743037</v>
+      </c>
+      <c r="DR6" t="n">
+        <v>-0.1285327585743037</v>
+      </c>
+      <c r="DS6" t="n">
+        <v>-0.1285327585743037</v>
+      </c>
+      <c r="DT6" t="n">
+        <v>-0.1285327585743037</v>
+      </c>
+      <c r="DU6" t="n">
+        <v>-0.1285327585743037</v>
+      </c>
+      <c r="DV6" t="n">
+        <v>-0.1285327585743037</v>
+      </c>
+      <c r="DW6" t="n">
+        <v>-0.1285327585743037</v>
+      </c>
+      <c r="DX6" t="n">
+        <v>-0.1285327585743037</v>
+      </c>
+      <c r="DY6" t="n">
+        <v>-0.1285327585743037</v>
+      </c>
+      <c r="DZ6" t="n">
+        <v>-0.1285327585743037</v>
+      </c>
+      <c r="EA6" t="n">
+        <v>-0.1285327585743046</v>
+      </c>
+      <c r="EB6" t="n">
+        <v>-0.1285327585743037</v>
+      </c>
+      <c r="EC6" t="n">
+        <v>-0.1285327585743037</v>
+      </c>
+      <c r="ED6" t="n">
+        <v>-0.1285327585743037</v>
+      </c>
+      <c r="EE6" t="n">
+        <v>-0.1285327585743037</v>
+      </c>
+      <c r="EF6" t="n">
+        <v>-0.1285327585743037</v>
+      </c>
+      <c r="EG6" t="n">
+        <v>-0.1285327585743037</v>
+      </c>
+      <c r="EH6" t="n">
+        <v>-0.1285327585743046</v>
+      </c>
+      <c r="EI6" t="n">
+        <v>-0.1285327585743037</v>
+      </c>
+      <c r="EJ6" t="n">
+        <v>-0.1285327585743037</v>
+      </c>
+      <c r="EK6" t="n">
+        <v>-0.1285327585743037</v>
+      </c>
+      <c r="EL6" t="n">
+        <v>-0.1285327585743037</v>
+      </c>
+      <c r="EM6" t="n">
+        <v>-0.1285327585743037</v>
+      </c>
+      <c r="EN6" t="n">
+        <v>-0.1285327585743037</v>
+      </c>
+      <c r="EO6" t="n">
+        <v>-0.1285327585743046</v>
+      </c>
+      <c r="EP6" t="n">
+        <v>-0.1285327585743046</v>
+      </c>
+      <c r="EQ6" t="n">
+        <v>-0.1285327585743046</v>
+      </c>
+      <c r="ER6" t="n">
+        <v>-0.1285327585743037</v>
+      </c>
+      <c r="ES6" t="n">
+        <v>-0.1285327585743037</v>
+      </c>
+      <c r="ET6" t="n">
+        <v>-0.1285327585743037</v>
+      </c>
+      <c r="EU6" t="n">
+        <v>-0.1285327585743037</v>
+      </c>
+      <c r="EV6" t="n">
+        <v>-0.1285327585743037</v>
+      </c>
+      <c r="EW6" t="n">
+        <v>-0.1285327585743037</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/annual/Lasso_Time_Dummy_Models_Annual.xlsx
+++ b/annual/Lasso_Time_Dummy_Models_Annual.xlsx
@@ -12,6 +12,7 @@
     <sheet name="Predictions_By_Product" sheetId="3" state="visible" r:id="rId3"/>
     <sheet name="Jevons_Indices" sheetId="4" state="visible" r:id="rId4"/>
     <sheet name="Model_Period_Matrix" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="Price_Change_R2" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -41179,4 +41180,113 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C7"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Period</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>R2_Price_Change</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Samples</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>2020 → 2021</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>2.220446049250313e-16</v>
+      </c>
+      <c r="C2" t="n">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>2021 → 2022</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C3" t="n">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>2022 → 2023</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>-2.220446049250313e-16</v>
+      </c>
+      <c r="C4" t="n">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>2023 → 2024</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C5" t="n">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>2024 → 2025</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>0</v>
+      </c>
+      <c r="C6" t="n">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Overall (Average)</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>0</v>
+      </c>
+      <c r="C7" t="n">
+        <v>413</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/annual/Lasso_Time_Dummy_Models_Annual.xlsx
+++ b/annual/Lasso_Time_Dummy_Models_Annual.xlsx
@@ -41215,7 +41215,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>2.220446049250313e-16</v>
+        <v>0</v>
       </c>
       <c r="C2" t="n">
         <v>24</v>
@@ -41241,7 +41241,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>-2.220446049250313e-16</v>
+        <v>0</v>
       </c>
       <c r="C4" t="n">
         <v>86</v>

--- a/annual/Lasso_Time_Dummy_Models_Annual.xlsx
+++ b/annual/Lasso_Time_Dummy_Models_Annual.xlsx
@@ -430,7 +430,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L6"/>
+  <dimension ref="A1:M6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -466,30 +466,35 @@
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
+          <t>Partial_R2_Time_Dummy</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
           <t>Alpha</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>Features_Selected</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>Jevons_Actual</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>Jevons_Predicted</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>Delta_Actual_%</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>Delta_Predicted_%</t>
         </is>
@@ -518,20 +523,23 @@
       <c r="F2" t="n">
         <v>0.8528034961505272</v>
       </c>
-      <c r="G2" t="inlineStr"/>
-      <c r="H2" t="n">
+      <c r="G2" t="n">
+        <v>0.2481526581175866</v>
+      </c>
+      <c r="H2" t="inlineStr"/>
+      <c r="I2" t="n">
         <v>10</v>
       </c>
-      <c r="I2" t="n">
+      <c r="J2" t="n">
         <v>-0.2757630034786271</v>
       </c>
-      <c r="J2" t="n">
+      <c r="K2" t="n">
         <v>-0.227379456215536</v>
       </c>
-      <c r="K2" t="n">
+      <c r="L2" t="n">
         <v>-27.57630034786271</v>
       </c>
-      <c r="L2" t="n">
+      <c r="M2" t="n">
         <v>-22.7379456215536</v>
       </c>
     </row>
@@ -558,20 +566,23 @@
       <c r="F3" t="n">
         <v>0.6002225945197304</v>
       </c>
-      <c r="G3" t="inlineStr"/>
-      <c r="H3" t="n">
+      <c r="G3" t="n">
+        <v>0.03740915817607893</v>
+      </c>
+      <c r="H3" t="inlineStr"/>
+      <c r="I3" t="n">
         <v>10</v>
       </c>
-      <c r="I3" t="n">
+      <c r="J3" t="n">
         <v>-0.3175129985302031</v>
       </c>
-      <c r="J3" t="n">
+      <c r="K3" t="n">
         <v>-0.1418017032069443</v>
       </c>
-      <c r="K3" t="n">
+      <c r="L3" t="n">
         <v>-31.75129985302031</v>
       </c>
-      <c r="L3" t="n">
+      <c r="M3" t="n">
         <v>-14.18017032069443</v>
       </c>
     </row>
@@ -598,20 +609,23 @@
       <c r="F4" t="n">
         <v>0.5538167191656747</v>
       </c>
-      <c r="G4" t="inlineStr"/>
-      <c r="H4" t="n">
+      <c r="G4" t="n">
+        <v>0.04946932341366694</v>
+      </c>
+      <c r="H4" t="inlineStr"/>
+      <c r="I4" t="n">
         <v>10</v>
       </c>
-      <c r="I4" t="n">
+      <c r="J4" t="n">
         <v>-0.248257212170003</v>
       </c>
-      <c r="J4" t="n">
+      <c r="K4" t="n">
         <v>-0.1717656642648218</v>
       </c>
-      <c r="K4" t="n">
+      <c r="L4" t="n">
         <v>-24.8257212170003</v>
       </c>
-      <c r="L4" t="n">
+      <c r="M4" t="n">
         <v>-17.17656642648218</v>
       </c>
     </row>
@@ -638,20 +652,23 @@
       <c r="F5" t="n">
         <v>0.5606055740750648</v>
       </c>
-      <c r="G5" t="inlineStr"/>
-      <c r="H5" t="n">
+      <c r="G5" t="n">
+        <v>0.04848751227999715</v>
+      </c>
+      <c r="H5" t="inlineStr"/>
+      <c r="I5" t="n">
         <v>10</v>
       </c>
-      <c r="I5" t="n">
+      <c r="J5" t="n">
         <v>-0.2305413621213246</v>
       </c>
-      <c r="J5" t="n">
+      <c r="K5" t="n">
         <v>-0.1717257086693703</v>
       </c>
-      <c r="K5" t="n">
+      <c r="L5" t="n">
         <v>-23.05413621213246</v>
       </c>
-      <c r="L5" t="n">
+      <c r="M5" t="n">
         <v>-17.17257086693703</v>
       </c>
     </row>
@@ -678,20 +695,23 @@
       <c r="F6" t="n">
         <v>0.545227720463719</v>
       </c>
-      <c r="G6" t="inlineStr"/>
-      <c r="H6" t="n">
+      <c r="G6" t="n">
+        <v>0.02675030274532975</v>
+      </c>
+      <c r="H6" t="inlineStr"/>
+      <c r="I6" t="n">
         <v>10</v>
       </c>
-      <c r="I6" t="n">
+      <c r="J6" t="n">
         <v>-0.1414529919696962</v>
       </c>
-      <c r="J6" t="n">
+      <c r="K6" t="n">
         <v>-0.1285327585743039</v>
       </c>
-      <c r="K6" t="n">
+      <c r="L6" t="n">
         <v>-14.14529919696962</v>
       </c>
-      <c r="L6" t="n">
+      <c r="M6" t="n">
         <v>-12.85327585743038</v>
       </c>
     </row>
